--- a/output/laminas_comunales/comunal_i_peringr_median_a_2024_araucania.xlsx
+++ b/output/laminas_comunales/comunal_i_peringr_median_a_2024_araucania.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -381,11 +381,6 @@
           <t>delta_pct</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>is_emph</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -405,9 +400,6 @@
       <c r="E2">
         <v>-2.936549554273726</v>
       </c>
-      <c r="F2" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -427,9 +419,6 @@
       <c r="E3">
         <v>6.427221172022679</v>
       </c>
-      <c r="F3" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -449,9 +438,6 @@
       <c r="E4">
         <v>0.1352569882777432</v>
       </c>
-      <c r="F4" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -471,9 +457,6 @@
       <c r="E5">
         <v>-9.154351395730709</v>
       </c>
-      <c r="F5" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -493,9 +476,6 @@
       <c r="E6">
         <v>10.20301926080167</v>
       </c>
-      <c r="F6" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -515,9 +495,6 @@
       <c r="E7">
         <v>-5.313351498637598</v>
       </c>
-      <c r="F7" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -537,9 +514,6 @@
       <c r="E8">
         <v>-6.471910112359557</v>
       </c>
-      <c r="F8" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -559,9 +533,6 @@
       <c r="E9">
         <v>-11.56222418358341</v>
       </c>
-      <c r="F9" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -581,9 +552,6 @@
       <c r="E10">
         <v>-1.549225387306363</v>
       </c>
-      <c r="F10" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -603,9 +571,6 @@
       <c r="E11">
         <v>-6.353055286129983</v>
       </c>
-      <c r="F11" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -625,9 +590,6 @@
       <c r="E12">
         <v>0.6929637526652321</v>
       </c>
-      <c r="F12" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -647,9 +609,6 @@
       <c r="E13">
         <v>-10.31434184675834</v>
       </c>
-      <c r="F13" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -669,9 +628,6 @@
       <c r="E14">
         <v>-6.82666666666667</v>
       </c>
-      <c r="F14" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -691,9 +647,6 @@
       <c r="E15">
         <v>-2.833530106257376</v>
       </c>
-      <c r="F15" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -713,9 +666,6 @@
       <c r="E16">
         <v>-11.27531472359058</v>
       </c>
-      <c r="F16" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -735,9 +685,6 @@
       <c r="E17">
         <v>-4.580606781677565</v>
       </c>
-      <c r="F17" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -757,9 +704,6 @@
       <c r="E18">
         <v>-9.236947791164651</v>
       </c>
-      <c r="F18" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -779,9 +723,6 @@
       <c r="E19">
         <v>-6.332931242460793</v>
       </c>
-      <c r="F19" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -801,9 +742,6 @@
       <c r="E20">
         <v>5.409153952843271</v>
       </c>
-      <c r="F20" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -823,9 +761,6 @@
       <c r="E21">
         <v>-15.47486033519552</v>
       </c>
-      <c r="F21" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -845,9 +780,6 @@
       <c r="E22">
         <v>-9.795673076923084</v>
       </c>
-      <c r="F22" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -867,9 +799,6 @@
       <c r="E23">
         <v>-3.744351194318918</v>
       </c>
-      <c r="F23" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -889,9 +818,6 @@
       <c r="E24">
         <v>-7.658779576587794</v>
       </c>
-      <c r="F24" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -911,9 +837,6 @@
       <c r="E25">
         <v>-6.20253164556962</v>
       </c>
-      <c r="F25" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -933,9 +856,6 @@
       <c r="E26">
         <v>-7.451471509079532</v>
       </c>
-      <c r="F26" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -955,9 +875,6 @@
       <c r="E27">
         <v>0.4929577464788837</v>
       </c>
-      <c r="F27" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -977,9 +894,6 @@
       <c r="E28">
         <v>-25.44378698224853</v>
       </c>
-      <c r="F28" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -999,9 +913,6 @@
       <c r="E29">
         <v>-12.1811224489796</v>
       </c>
-      <c r="F29" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1021,9 +932,6 @@
       <c r="E30">
         <v>-3.913347309573723</v>
       </c>
-      <c r="F30" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1043,9 +951,6 @@
       <c r="E31">
         <v>-6.824712643678154</v>
       </c>
-      <c r="F31" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1065,9 +970,6 @@
       <c r="E32">
         <v>-6.756756756756754</v>
       </c>
-      <c r="F32" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1086,9 +988,6 @@
       </c>
       <c r="E33">
         <v>-5.300077942322678</v>
-      </c>
-      <c r="F33" t="b">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
